--- a/data/trans_dic/P25A$voluntad-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25A$voluntad-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>56,81; 72,86</t>
+          <t>56,39; 73,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,6; 81,61</t>
+          <t>68,86; 81,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,0; 72,39</t>
+          <t>55,0; 73,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60,35; 86,16</t>
+          <t>59,25; 86,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,18; 95,72</t>
+          <t>81,24; 95,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,44; 78,13</t>
+          <t>53,04; 77,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,94; 73,7</t>
+          <t>59,52; 73,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74,51; 84,87</t>
+          <t>74,47; 84,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56,53; 72,28</t>
+          <t>57,49; 71,92</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,98; 63,48</t>
+          <t>49,13; 64,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60,47; 72,56</t>
+          <t>60,01; 72,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,61; 67,73</t>
+          <t>52,47; 67,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,97; 80,79</t>
+          <t>57,63; 80,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,81; 78,19</t>
+          <t>60,29; 79,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,19; 80,39</t>
+          <t>61,61; 80,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,95; 65,84</t>
+          <t>54,33; 66,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>62,53; 72,52</t>
+          <t>61,84; 72,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57,74; 69,71</t>
+          <t>57,86; 70,09</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48,94; 66,29</t>
+          <t>48,36; 65,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,62; 71,25</t>
+          <t>54,91; 71,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,77; 57,02</t>
+          <t>39,7; 57,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,74; 78,82</t>
+          <t>51,83; 79,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69,32; 85,68</t>
+          <t>69,1; 85,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,66; 77,51</t>
+          <t>57,23; 78,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,71; 67,27</t>
+          <t>51,11; 66,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63,07; 75,02</t>
+          <t>62,52; 73,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,05; 62,27</t>
+          <t>47,66; 61,68</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,32; 60,63</t>
+          <t>45,94; 60,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,78; 70,69</t>
+          <t>56,7; 70,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,4; 72,36</t>
+          <t>58,15; 72,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,46; 70,46</t>
+          <t>50,03; 70,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,16; 82,82</t>
+          <t>65,73; 82,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,27; 80,53</t>
+          <t>61,81; 79,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,0; 60,97</t>
+          <t>49,37; 61,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,33; 72,93</t>
+          <t>62,53; 73,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,23; 73,22</t>
+          <t>62,68; 73,72</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>53,55; 61,28</t>
+          <t>53,56; 61,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,17; 70,85</t>
+          <t>63,84; 70,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56,39; 64,1</t>
+          <t>56,27; 64,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,98; 72,58</t>
+          <t>60,04; 72,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>72,9; 81,84</t>
+          <t>72,97; 81,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,35; 74,91</t>
+          <t>64,57; 74,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,52; 63,28</t>
+          <t>56,57; 63,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>67,85; 73,29</t>
+          <t>67,77; 73,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60,47; 66,96</t>
+          <t>60,43; 66,62</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, por propia voluntad (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>73534; 94312</t>
+          <t>72985; 94605</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>131304; 153956</t>
+          <t>129913; 154040</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65010; 85570</t>
+          <t>65010; 86716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24924; 35583</t>
+          <t>24471; 35524</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>58519; 69001</t>
+          <t>58566; 69085</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27679; 42036</t>
+          <t>28537; 41574</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>102329; 125830</t>
+          <t>101629; 126214</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>194290; 221280</t>
+          <t>194171; 221046</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>97233; 124339</t>
+          <t>98892; 123719</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91526; 118618</t>
+          <t>91804; 119996</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>150383; 180463</t>
+          <t>149240; 179162</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95027; 120056</t>
+          <t>93017; 120032</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45373; 62154</t>
+          <t>44339; 62015</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57820; 76875</t>
+          <t>59273; 77947</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51964; 69399</t>
+          <t>53193; 69410</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>142314; 173673</t>
+          <t>143312; 176282</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>216973; 251647</t>
+          <t>214584; 251335</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>152191; 183752</t>
+          <t>152503; 184761</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>65729; 89022</t>
+          <t>64952; 88512</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92418; 122805</t>
+          <t>94631; 122736</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53102; 76146</t>
+          <t>53011; 76508</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19737; 31279</t>
+          <t>20567; 31545</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>71517; 88395</t>
+          <t>71288; 88664</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41498; 57791</t>
+          <t>42672; 58371</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91700; 117038</t>
+          <t>88928; 115973</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>173767; 206685</t>
+          <t>172265; 203312</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>99986; 129583</t>
+          <t>99177; 128347</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>80595; 105485</t>
+          <t>79932; 105867</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>117176; 145893</t>
+          <t>117011; 145898</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>103075; 127712</t>
+          <t>102623; 128263</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45905; 65395</t>
+          <t>46438; 65064</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>74747; 93570</t>
+          <t>74259; 93143</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76623; 97529</t>
+          <t>74856; 96135</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>133397; 162662</t>
+          <t>131726; 163654</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>199052; 232906</t>
+          <t>199706; 234163</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>185188; 217888</t>
+          <t>186539; 219383</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>334485; 382759</t>
+          <t>334505; 382484</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>523706; 578177</t>
+          <t>520980; 577329</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>341428; 388135</t>
+          <t>340682; 387723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150391; 181985</t>
+          <t>150536; 181390</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>281802; 316349</t>
+          <t>282067; 314939</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>216088; 251543</t>
+          <t>216823; 250636</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>494708; 553869</t>
+          <t>495184; 552332</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>816026; 881413</t>
+          <t>815047; 880525</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>569218; 630305</t>
+          <t>568845; 627130</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$voluntad-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25A$voluntad-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>56,39; 73,09</t>
+          <t>55,85; 72,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,86; 81,65</t>
+          <t>69,3; 81,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,0; 73,36</t>
+          <t>55,22; 72,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,25; 86,02</t>
+          <t>58,51; 85,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,24; 95,84</t>
+          <t>80,79; 95,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,04; 77,27</t>
+          <t>51,92; 78,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,52; 73,92</t>
+          <t>59,61; 73,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74,47; 84,78</t>
+          <t>74,63; 84,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,49; 71,92</t>
+          <t>57,05; 71,72</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,13; 64,22</t>
+          <t>48,98; 64,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60,01; 72,04</t>
+          <t>59,51; 72,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,47; 67,71</t>
+          <t>53,09; 67,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57,63; 80,6</t>
+          <t>58,86; 81,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,29; 79,28</t>
+          <t>59,49; 77,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,61; 80,4</t>
+          <t>61,5; 81,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,33; 66,83</t>
+          <t>53,87; 66,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>61,84; 72,43</t>
+          <t>61,97; 72,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57,86; 70,09</t>
+          <t>57,74; 70,0</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48,36; 65,91</t>
+          <t>48,8; 65,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54,91; 71,21</t>
+          <t>55,53; 70,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,7; 57,29</t>
+          <t>39,49; 57,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,83; 79,49</t>
+          <t>48,79; 78,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69,1; 85,94</t>
+          <t>69,85; 86,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57,23; 78,29</t>
+          <t>56,76; 77,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,11; 66,66</t>
+          <t>52,15; 67,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>62,52; 73,79</t>
+          <t>63,12; 74,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47,66; 61,68</t>
+          <t>48,56; 62,47</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,94; 60,85</t>
+          <t>45,2; 60,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,7; 70,7</t>
+          <t>55,49; 70,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,15; 72,67</t>
+          <t>59,08; 72,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,03; 70,1</t>
+          <t>49,51; 69,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,73; 82,44</t>
+          <t>66,41; 83,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,81; 79,38</t>
+          <t>63,2; 79,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,37; 61,34</t>
+          <t>49,76; 61,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,53; 73,32</t>
+          <t>62,35; 73,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,68; 73,72</t>
+          <t>62,45; 73,54</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>53,56; 61,24</t>
+          <t>53,85; 61,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63,84; 70,74</t>
+          <t>63,91; 70,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56,27; 64,03</t>
+          <t>56,33; 63,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60,04; 72,34</t>
+          <t>60,06; 71,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>72,97; 81,47</t>
+          <t>73,32; 81,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,57; 74,64</t>
+          <t>65,07; 74,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,57; 63,1</t>
+          <t>56,47; 63,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>67,77; 73,22</t>
+          <t>67,98; 73,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60,43; 66,62</t>
+          <t>60,28; 66,77</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72985; 94605</t>
+          <t>72291; 93515</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>129913; 154040</t>
+          <t>130746; 154059</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65010; 86716</t>
+          <t>65272; 86022</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24471; 35524</t>
+          <t>24163; 35418</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>58566; 69085</t>
+          <t>58240; 68873</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28537; 41574</t>
+          <t>27937; 42485</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>101629; 126214</t>
+          <t>101770; 126216</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>194171; 221046</t>
+          <t>194595; 219527</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>98892; 123719</t>
+          <t>98138; 123375</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91804; 119996</t>
+          <t>91524; 120690</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>149240; 179162</t>
+          <t>147994; 179902</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93017; 120032</t>
+          <t>94111; 120102</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44339; 62015</t>
+          <t>45282; 62480</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59273; 77947</t>
+          <t>58495; 76452</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53193; 69410</t>
+          <t>53096; 70066</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>143312; 176282</t>
+          <t>142112; 174884</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>214584; 251335</t>
+          <t>215059; 251645</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>152503; 184761</t>
+          <t>152192; 184516</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64952; 88512</t>
+          <t>65533; 88546</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94631; 122736</t>
+          <t>95708; 121883</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53011; 76508</t>
+          <t>52735; 76554</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20567; 31545</t>
+          <t>19360; 31141</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>71288; 88664</t>
+          <t>72066; 89335</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42672; 58371</t>
+          <t>42320; 57959</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88928; 115973</t>
+          <t>90728; 117025</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>172265; 203312</t>
+          <t>173925; 206124</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>99177; 128347</t>
+          <t>101063; 129992</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>79932; 105867</t>
+          <t>78647; 105923</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>117011; 145898</t>
+          <t>114512; 144930</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102623; 128263</t>
+          <t>104273; 127465</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46438; 65064</t>
+          <t>45949; 64902</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>74259; 93143</t>
+          <t>75029; 94033</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74856; 96135</t>
+          <t>76545; 96726</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>131726; 163654</t>
+          <t>132769; 164815</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>199706; 234163</t>
+          <t>199113; 234014</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>186539; 219383</t>
+          <t>185849; 218839</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>334505; 382484</t>
+          <t>336313; 385026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>520980; 577329</t>
+          <t>521546; 576324</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>340682; 387723</t>
+          <t>341105; 387069</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150536; 181390</t>
+          <t>150598; 180176</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>282067; 314939</t>
+          <t>283419; 315071</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>216823; 250636</t>
+          <t>218497; 250987</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>495184; 552332</t>
+          <t>494299; 553554</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>815047; 880525</t>
+          <t>817611; 883544</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>568845; 627130</t>
+          <t>567445; 628504</t>
         </is>
       </c>
     </row>
